--- a/main/StructureDefinition-Provenance.xlsx
+++ b/main/StructureDefinition-Provenance.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2511" uniqueCount="438">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2511" uniqueCount="437">
   <si>
     <t>Property</t>
   </si>
@@ -374,7 +374,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/languages</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -579,7 +579,7 @@
     <t>Aa resource (or, for logical models, the URI of the logical model).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/resource-types|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/resource-types</t>
   </si>
   <si>
     <t>Reference.type</t>
@@ -702,7 +702,7 @@
     <t>Provenance.location</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Location|4.0.1)
+    <t xml:space="preserve">Reference(Location)
 </t>
   </si>
   <si>
@@ -773,7 +773,7 @@
     <t>The activity that took place.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/provenance-activity-type|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/provenance-activity-type</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -855,7 +855,7 @@
     <t>The type of participation that a provenance agent played with respect to the activity.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/provenance-agent-type|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/provenance-agent-type</t>
   </si>
   <si>
     <t>Event.performer.function</t>
@@ -888,7 +888,7 @@
     <t>The role that a provenance agent played with respect to the activity.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-role-type|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/security-role-type</t>
   </si>
   <si>
     <t>.typecode</t>
@@ -900,7 +900,7 @@
     <t>Provenance.agent.who</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|RelatedPerson|4.0.1|Patient|4.0.1|Device|4.0.1|Organization|4.0.1)
+    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|RelatedPerson|Patient|Device|Organization)
 </t>
   </si>
   <si>
@@ -1161,9 +1161,6 @@
   </si>
   <si>
     <t>Examples include attesting to: authorship, correct transcription, and witness of specific event. Also known as a &amp;quot;Commitment Type Indication&amp;quot;.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/signature-type|4.0.1</t>
   </si>
   <si>
     <t>Signature.type</t>
@@ -1718,7 +1715,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="68.2109375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="46.74609375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="45.015625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -7989,25 +7986,25 @@
       </c>
       <c r="Y54" s="2"/>
       <c r="Z54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF54" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="AA54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF54" t="s" s="2">
-        <v>370</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>90</v>
@@ -8039,10 +8036,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8154,10 +8151,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8271,10 +8268,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8300,16 +8297,16 @@
         <v>104</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>374</v>
       </c>
-      <c r="M57" t="s" s="2">
+      <c r="N57" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="N57" t="s" s="2">
+      <c r="O57" t="s" s="2">
         <v>376</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>377</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>21</v>
@@ -8358,7 +8355,7 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8376,7 +8373,7 @@
         <v>21</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>21</v>
@@ -8390,10 +8387,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8419,13 +8416,13 @@
         <v>157</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>381</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>382</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>383</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8475,7 +8472,7 @@
         <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8493,7 +8490,7 @@
         <v>21</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>21</v>
@@ -8507,10 +8504,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8536,14 +8533,14 @@
         <v>110</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>387</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>388</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>21</v>
@@ -8592,7 +8589,7 @@
         <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -8610,7 +8607,7 @@
         <v>21</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>21</v>
@@ -8624,10 +8621,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8653,14 +8650,14 @@
         <v>157</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>394</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>21</v>
@@ -8709,7 +8706,7 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -8727,7 +8724,7 @@
         <v>21</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>21</v>
@@ -8741,10 +8738,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8767,19 +8764,19 @@
         <v>91</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="L61" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="L61" t="s" s="2">
+      <c r="M61" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="M61" t="s" s="2">
+      <c r="N61" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="N61" t="s" s="2">
+      <c r="O61" t="s" s="2">
         <v>402</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>403</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>21</v>
@@ -8828,7 +8825,7 @@
         <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -8846,7 +8843,7 @@
         <v>21</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>21</v>
@@ -8860,10 +8857,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8889,13 +8886,13 @@
         <v>204</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="N62" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>409</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -8945,7 +8942,7 @@
         <v>21</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>90</v>
@@ -8977,10 +8974,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9006,13 +9003,13 @@
         <v>283</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="M63" t="s" s="2">
-        <v>413</v>
-      </c>
       <c r="N63" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9062,7 +9059,7 @@
         <v>21</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>90</v>
@@ -9094,10 +9091,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9123,16 +9120,16 @@
         <v>283</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>416</v>
       </c>
-      <c r="M64" t="s" s="2">
+      <c r="N64" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="N64" t="s" s="2">
+      <c r="O64" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>419</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>21</v>
@@ -9181,7 +9178,7 @@
         <v>21</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9213,10 +9210,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9242,13 +9239,13 @@
         <v>110</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="M65" t="s" s="2">
+      <c r="N65" t="s" s="2">
         <v>423</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>424</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9277,28 +9274,28 @@
         <v>308</v>
       </c>
       <c r="Y65" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="Z65" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="Z65" t="s" s="2">
+      <c r="AA65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF65" t="s" s="2">
         <v>426</v>
-      </c>
-      <c r="AA65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF65" t="s" s="2">
-        <v>427</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -9330,10 +9327,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9359,10 +9356,10 @@
         <v>110</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>430</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9392,11 +9389,11 @@
         <v>308</v>
       </c>
       <c r="Y66" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="Z66" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="Z66" t="s" s="2">
-        <v>426</v>
-      </c>
       <c r="AA66" t="s" s="2">
         <v>21</v>
       </c>
@@ -9413,7 +9410,7 @@
         <v>21</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -9445,10 +9442,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9471,16 +9468,16 @@
         <v>21</v>
       </c>
       <c r="K67" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="L67" t="s" s="2">
         <v>433</v>
       </c>
-      <c r="L67" t="s" s="2">
+      <c r="M67" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="M67" t="s" s="2">
+      <c r="N67" t="s" s="2">
         <v>435</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>436</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9530,7 +9527,7 @@
         <v>21</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
